--- a/results/trace_final20_temp06_seed42_vero-qwen25-7b_20260714T192431Z_results.xlsx
+++ b/results/trace_final20_temp06_seed42_vero-qwen25-7b_20260714T192431Z_results.xlsx
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23.5445205479452</v>
+        <v>27.91095890410959</v>
       </c>
       <c r="F9" t="n">
         <v>1168</v>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.5445205479452</v>
+        <v>27.91095890410959</v>
       </c>
       <c r="I9" t="n">
         <v>1168</v>
